--- a/samples/imagin_ejemplo.xlsx
+++ b/samples/imagin_ejemplo.xlsx
@@ -1,141 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://udlcat-my.sharepoint.com/personal/ggp10_alumnes_udl_cat/Documents/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="11_00281C7F2E7BDF60EF7F840FD4B74FAAF1DE230A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97234A71-2D51-40DF-AEA4-DE077CB72103}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
+    <sheet name="Worksheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
-  <si>
-    <t>Concepto</t>
-  </si>
-  <si>
-    <t>Fecha</t>
-  </si>
-  <si>
-    <t>Importe</t>
-  </si>
-  <si>
-    <t>Saldo</t>
-  </si>
-  <si>
-    <t>BIZUM ENVIAT</t>
-  </si>
-  <si>
-    <t>WWW.AMAZON</t>
-  </si>
-  <si>
-    <t>29/09/2026</t>
-  </si>
-  <si>
-    <t>-69,73EUR</t>
-  </si>
-  <si>
-    <t>56,96EUR</t>
-  </si>
-  <si>
-    <t>BIZUM REBUT</t>
-  </si>
-  <si>
-    <t>27/09/2026</t>
-  </si>
-  <si>
-    <t>-8,20EUR</t>
-  </si>
-  <si>
-    <t>26/09/2026</t>
-  </si>
-  <si>
-    <t>2,00EUR</t>
-  </si>
-  <si>
-    <t>65,16EUR</t>
-  </si>
-  <si>
-    <t>BON AREA</t>
-  </si>
-  <si>
-    <t>-1,94EUR</t>
-  </si>
-  <si>
-    <t>63,16EUR</t>
-  </si>
-  <si>
-    <t>MERCADONA</t>
-  </si>
-  <si>
-    <t>-23EUR</t>
-  </si>
-  <si>
-    <t>-2,45EUR</t>
-  </si>
-  <si>
-    <t>40,16EUR</t>
-  </si>
-  <si>
-    <t>37,71EUR</t>
-  </si>
-  <si>
-    <t>-0,5EUR</t>
-  </si>
-  <si>
-    <t>37,12EUR</t>
-  </si>
-  <si>
-    <t>enviament de dine</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
+      <name val="Calibri"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF242424"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color rgb="FF242424"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -154,24 +50,83 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="1" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -461,129 +416,218 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.42578125" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col width="18.42578125" customWidth="1" min="1" max="1"/>
+    <col width="10.7109375" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="11.85546875" bestFit="1" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="1">
-        <v>46292</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="1">
-        <v>46292</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="1">
-        <v>46296</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" t="s">
-        <v>24</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Concepto</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Importe</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Saldo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>WWW.AMAZON</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>-69,73EUR</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>67,23EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BIZUM ENVIAT</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>27/09/2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>-8,20EUR</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>136,96EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>enviament de dine</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>27/09/2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>-50,00EUR</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>145,16EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MERCADONA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>27/09/2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>-2,45EUR</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>195,16EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MERCADONA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>27/09/2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>-2,45EUR</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>197,61EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BIZUM REBUT</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>26/09/2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2,00EUR</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>200,06EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BON AREA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>26/09/2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>-1,94EUR</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>198,06EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TRANSFER IMMEDIATA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>150,00EUR</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>200,00EUR</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>